--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -504,7 +504,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -516,7 +518,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -528,7 +532,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
+++ b/main/ig/CodeSystem-fr-core-cs-location-position-room.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
